--- a/src/test/resources/data/ApiDataTest.xlsx
+++ b/src/test/resources/data/ApiDataTest.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhosimar\Documents\PROYECTO AUTO\qa-automation-serenity-screenplay\src\test\resources\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhosimar\Documents\PROYECTO AUTO\RAMA GIT\qa-automation-serenity-screenplay\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6497B3C8-29BB-4E51-9563-01659CFA6848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349921B4-EB7C-4261-A6A7-C8A7BD7C4FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -907,7 +907,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
